--- a/PREUBA/nuevo.xlsx
+++ b/PREUBA/nuevo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\munozi\Desktop\PREUBA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\munozi\Desktop\nuevo programa\PREUBA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -190,9 +190,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="\$\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -213,6 +213,12 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -286,10 +292,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -315,9 +322,10 @@
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="31"/>
     </xf>
@@ -329,9 +337,13 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -633,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="15.1640625" style="6" customWidth="1"/>
@@ -641,46 +653,40 @@
     <col min="3" max="4" width="17.33203125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="16">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8">
+      <c r="C2" s="8">
         <v>46113</v>
       </c>
-      <c r="D1" s="9">
+      <c r="D2" s="9">
         <v>46143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A2" s="1">
-        <v>180103</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3">
-        <v>6565.58</v>
-      </c>
-      <c r="D2" s="3">
-        <v>6696.89</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="1">
-        <v>180104</v>
+        <v>180103</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3">
-        <v>7178.57</v>
+        <v>6565.58</v>
       </c>
       <c r="D3" s="3">
-        <v>7322.14</v>
+        <v>6696.89</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
@@ -688,7 +694,7 @@
         <v>180104</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3">
         <v>7178.57</v>
@@ -699,16 +705,16 @@
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
       <c r="A5" s="1">
-        <v>180106</v>
+        <v>180104</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3">
-        <v>11057.93</v>
+        <v>7178.57</v>
       </c>
       <c r="D5" s="3">
-        <v>11279.09</v>
+        <v>7322.14</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1">
@@ -716,7 +722,7 @@
         <v>180106</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3">
         <v>11057.93</v>
@@ -727,44 +733,44 @@
     </row>
     <row r="7" spans="1:4" ht="16.5" customHeight="1">
       <c r="A7" s="1">
-        <v>180107</v>
+        <v>180106</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="3">
-        <v>11761.64</v>
+        <v>11057.93</v>
       </c>
       <c r="D7" s="3">
-        <v>11996.87</v>
+        <v>11279.09</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1">
       <c r="A8" s="1">
-        <v>180109</v>
+        <v>180107</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="3">
-        <v>5194.07</v>
+        <v>11761.64</v>
       </c>
       <c r="D8" s="3">
-        <v>5297.95</v>
+        <v>11996.87</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" customHeight="1">
       <c r="A9" s="1">
-        <v>180110</v>
+        <v>180109</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="3">
-        <v>7371.83</v>
+        <v>5194.07</v>
       </c>
       <c r="D9" s="3">
-        <v>7519.27</v>
+        <v>5297.95</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5" customHeight="1">
@@ -772,7 +778,7 @@
         <v>180110</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3">
         <v>7371.83</v>
@@ -783,16 +789,16 @@
     </row>
     <row r="11" spans="1:4" ht="16.5" customHeight="1">
       <c r="A11" s="1">
-        <v>180112</v>
+        <v>180110</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3">
-        <v>15385.14</v>
+        <v>7371.83</v>
       </c>
       <c r="D11" s="3">
-        <v>15692.84</v>
+        <v>7519.27</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16.5" customHeight="1">
@@ -800,7 +806,7 @@
         <v>180112</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3">
         <v>15385.14</v>
@@ -811,142 +817,142 @@
     </row>
     <row r="13" spans="1:4" ht="16.5" customHeight="1">
       <c r="A13" s="1">
-        <v>180113</v>
+        <v>180112</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3">
-        <v>8407.06</v>
+        <v>15385.14</v>
       </c>
       <c r="D13" s="3">
-        <v>8575.2000000000007</v>
+        <v>15692.84</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16.5" customHeight="1">
       <c r="A14" s="1">
-        <v>180114</v>
+        <v>180113</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="3">
-        <v>10097.82</v>
+        <v>8407.06</v>
       </c>
       <c r="D14" s="3">
-        <v>10299.780000000001</v>
+        <v>8575.2000000000007</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16.5" customHeight="1">
       <c r="A15" s="1">
-        <v>180116</v>
+        <v>180114</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="3">
-        <v>12660.33</v>
+        <v>10097.82</v>
       </c>
       <c r="D15" s="3">
-        <v>12913.54</v>
+        <v>10299.780000000001</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16.5" customHeight="1">
       <c r="A16" s="1">
-        <v>185003</v>
+        <v>180116</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3">
-        <v>13673.27</v>
+        <v>12660.33</v>
       </c>
       <c r="D16" s="3">
-        <v>13946.74</v>
+        <v>12913.54</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="16.5" customHeight="1">
       <c r="A17" s="1">
-        <v>185004</v>
+        <v>185003</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="3">
-        <v>16132.63</v>
+        <v>13673.27</v>
       </c>
       <c r="D17" s="3">
-        <v>16455.28</v>
+        <v>13946.74</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="16.5" customHeight="1">
       <c r="A18" s="1">
-        <v>185012</v>
+        <v>185004</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="3">
-        <v>17645</v>
+        <v>16132.63</v>
       </c>
       <c r="D18" s="3">
-        <v>17997.900000000001</v>
+        <v>16455.28</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.5" customHeight="1">
       <c r="A19" s="1">
-        <v>185013</v>
+        <v>185012</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" s="3">
-        <v>17508.439999999999</v>
+        <v>17645</v>
       </c>
       <c r="D19" s="3">
-        <v>17858.61</v>
+        <v>17997.900000000001</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="16.5" customHeight="1">
       <c r="A20" s="1">
-        <v>185055</v>
+        <v>185013</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" s="3">
-        <v>26957.29</v>
+        <v>17508.439999999999</v>
       </c>
       <c r="D20" s="3">
-        <v>27496.44</v>
+        <v>17858.61</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="16.5" customHeight="1">
       <c r="A21" s="1">
-        <v>185057</v>
+        <v>185055</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" s="3">
-        <v>25016.5</v>
+        <v>26957.29</v>
       </c>
       <c r="D21" s="3">
-        <v>25516.83</v>
+        <v>27496.44</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.5" customHeight="1">
       <c r="A22" s="1">
-        <v>185058</v>
+        <v>185057</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" s="3">
-        <v>25766.880000000001</v>
+        <v>25016.5</v>
       </c>
       <c r="D22" s="3">
-        <v>26282.22</v>
+        <v>25516.83</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="16.5" customHeight="1">
@@ -954,7 +960,7 @@
         <v>185058</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="3">
         <v>25766.880000000001</v>
@@ -968,7 +974,7 @@
         <v>185058</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="3">
         <v>25766.880000000001</v>
@@ -979,44 +985,44 @@
     </row>
     <row r="25" spans="1:4" ht="16.5" customHeight="1">
       <c r="A25" s="1">
-        <v>185059</v>
+        <v>185058</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="3">
-        <v>34020.28</v>
+        <v>25766.880000000001</v>
       </c>
       <c r="D25" s="3">
-        <v>34700.69</v>
+        <v>26282.22</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="16.5" customHeight="1">
       <c r="A26" s="1">
-        <v>185060</v>
+        <v>185059</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="3">
-        <v>26957.29</v>
+        <v>34020.28</v>
       </c>
       <c r="D26" s="3">
-        <v>27496.44</v>
+        <v>34700.69</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="16.5" customHeight="1">
       <c r="A27" s="1">
-        <v>185063</v>
+        <v>185060</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="3">
-        <v>26957.279999999999</v>
+        <v>26957.29</v>
       </c>
       <c r="D27" s="3">
-        <v>27496.43</v>
+        <v>27496.44</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="16.5" customHeight="1">
@@ -1024,7 +1030,7 @@
         <v>185063</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="3">
         <v>26957.279999999999</v>
@@ -1038,7 +1044,7 @@
         <v>185063</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" s="3">
         <v>26957.279999999999</v>
@@ -1049,16 +1055,16 @@
     </row>
     <row r="30" spans="1:4" ht="16.5" customHeight="1">
       <c r="A30" s="1">
-        <v>185096</v>
+        <v>185063</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="3">
-        <v>26957.29</v>
+        <v>26957.279999999999</v>
       </c>
       <c r="D30" s="3">
-        <v>27496.44</v>
+        <v>27496.43</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="16.5" customHeight="1">
@@ -1066,7 +1072,7 @@
         <v>185096</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" s="3">
         <v>26957.29</v>
@@ -1080,7 +1086,7 @@
         <v>185096</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="3">
         <v>26957.29</v>
@@ -1094,7 +1100,7 @@
         <v>185096</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="3">
         <v>26957.29</v>
@@ -1108,7 +1114,7 @@
         <v>185096</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="3">
         <v>26957.29</v>
@@ -1122,7 +1128,7 @@
         <v>185096</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" s="3">
         <v>26957.29</v>
@@ -1133,10 +1139,10 @@
     </row>
     <row r="36" spans="1:4" ht="16.5" customHeight="1">
       <c r="A36" s="1">
-        <v>185217</v>
+        <v>185096</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="3">
         <v>26957.29</v>
@@ -1147,10 +1153,10 @@
     </row>
     <row r="37" spans="1:4" ht="16.5" customHeight="1">
       <c r="A37" s="1">
-        <v>185701</v>
+        <v>185217</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="3">
         <v>26957.29</v>
@@ -1164,7 +1170,7 @@
         <v>185701</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" s="3">
         <v>26957.29</v>
@@ -1174,59 +1180,59 @@
       </c>
     </row>
     <row r="39" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="1">
+        <v>185701</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" s="3">
+        <v>26957.29</v>
+      </c>
+      <c r="D39" s="3">
+        <v>27496.44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A40" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B40" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="14.1" customHeight="1">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="3"/>
-    </row>
-    <row r="41" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A41" s="12" t="s">
+    <row r="41" spans="1:4" ht="14.1" customHeight="1">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="3"/>
+    </row>
+    <row r="42" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A42" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="3"/>
-    </row>
-    <row r="42" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A42" s="1">
-        <v>185062</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="3">
-        <v>70917.34</v>
-      </c>
-      <c r="D42" s="3">
-        <v>72335.69</v>
-      </c>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="3"/>
     </row>
     <row r="43" spans="1:4" ht="16.5" customHeight="1">
       <c r="A43" s="1">
-        <v>188006</v>
+        <v>185062</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C43" s="3">
-        <v>133491.91</v>
+        <v>70917.34</v>
       </c>
       <c r="D43" s="3">
-        <v>136161.75</v>
+        <v>72335.69</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="16.5" customHeight="1">
@@ -1234,7 +1240,7 @@
         <v>188006</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44" s="3">
         <v>133491.91</v>
@@ -1245,16 +1251,16 @@
     </row>
     <row r="45" spans="1:4" ht="16.5" customHeight="1">
       <c r="A45" s="1">
-        <v>188004</v>
+        <v>188006</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" s="3">
-        <v>42556.19</v>
+        <v>133491.91</v>
       </c>
       <c r="D45" s="3">
-        <v>43407.31</v>
+        <v>136161.75</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="16.5" customHeight="1">
@@ -1262,7 +1268,7 @@
         <v>188004</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" s="3">
         <v>42556.19</v>
@@ -1271,40 +1277,40 @@
         <v>43407.31</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="14.1" customHeight="1">
-      <c r="A47" s="5"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A48" s="10" t="s">
+    <row r="47" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A47" s="1">
+        <v>188004</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" s="3">
+        <v>42556.19</v>
+      </c>
+      <c r="D47" s="3">
+        <v>43407.31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="14.1" customHeight="1">
+      <c r="A48" s="5"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="3"/>
+    </row>
+    <row r="49" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A49" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="3"/>
-    </row>
-    <row r="49" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A49" s="1">
-        <v>185103</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C49" s="3">
-        <v>60372.27</v>
-      </c>
-      <c r="D49" s="3">
-        <v>61579.72</v>
-      </c>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="3"/>
     </row>
     <row r="50" spans="1:4" ht="16.5" customHeight="1">
       <c r="A50" s="1">
         <v>185103</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C50" s="3">
         <v>60372.27</v>
@@ -1313,10 +1319,24 @@
         <v>61579.72</v>
       </c>
     </row>
+    <row r="51" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A51" s="1">
+        <v>185103</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51" s="3">
+        <v>60372.27</v>
+      </c>
+      <c r="D51" s="3">
+        <v>61579.72</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A42:C42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1341,11 +1361,11 @@
       <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13">
+      <c r="C1" s="14">
         <v>46113</v>
       </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" ht="16.5" customHeight="1">
       <c r="A2" s="7"/>
@@ -2050,11 +2070,11 @@
       <c r="C41" s="5"/>
     </row>
     <row r="42" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
     </row>
     <row r="43" spans="1:5" ht="16.5" customHeight="1">
       <c r="A43" s="1">
@@ -2117,11 +2137,11 @@
       <c r="C48" s="5"/>
     </row>
     <row r="49" spans="1:3" ht="16.5" customHeight="1">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
     </row>
     <row r="50" spans="1:3" ht="16.5" customHeight="1">
       <c r="A50" s="1">
